--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_2_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_2_bus.xlsx
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9380319009554192</v>
+        <v>0.938031900955419</v>
       </c>
       <c r="G2">
-        <v>-1.130199521952454</v>
+        <v>-1.130199521952451</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.2917056037382965</v>
+        <v>0.2917056037382951</v>
       </c>
       <c r="G3">
-        <v>-29.1713773552604</v>
+        <v>-29.17137735526048</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -572,22 +572,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.28296261028849</v>
+        <v>4.282962610288495</v>
       </c>
       <c r="C4">
-        <v>148.3661769587497</v>
+        <v>148.3661769587499</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354127</v>
+        <v>0.6277319163354117</v>
       </c>
       <c r="E4">
-        <v>2.898438697960062</v>
+        <v>2.898438697960059</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>77.77984578051343</v>
+        <v>77.77984578051344</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -808,16 +808,16 @@
         <v>1.031611214669993</v>
       </c>
       <c r="O3">
-        <v>0.2917056037512938</v>
+        <v>0.2917056037512941</v>
       </c>
       <c r="P3">
         <v>0.8906876332644386</v>
       </c>
       <c r="Q3">
-        <v>7.091324389062538</v>
+        <v>7.091324389062574</v>
       </c>
       <c r="R3">
-        <v>-119.1713773550799</v>
+        <v>-119.1713773550798</v>
       </c>
       <c r="S3">
         <v>171.7794727726615</v>
@@ -831,28 +831,28 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.709154423937069</v>
+        <v>3.709154423937071</v>
       </c>
       <c r="D4">
-        <v>3.709154423937069</v>
+        <v>3.709154423937071</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>42.82962610251916</v>
+        <v>42.82962610251919</v>
       </c>
       <c r="G4">
-        <v>42.82962610251916</v>
+        <v>42.82962610251919</v>
       </c>
       <c r="H4">
         <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162197</v>
+        <v>0.6277319163162202</v>
       </c>
       <c r="K4">
         <v>2.898438697979807</v>
@@ -873,7 +873,7 @@
         <v>0.952627964804756</v>
       </c>
       <c r="Q4">
-        <v>-1.251603637213732E-11</v>
+        <v>-1.247393797355009E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000115829802</v>
+        <v>0.9526279646110868</v>
       </c>
       <c r="O5">
-        <v>0.5500000122512995</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.10000002383428</v>
+        <v>0.9526279649968784</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999965509</v>
+        <v>1.148862771624108E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999965524</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>7.411950576426397E-13</v>
+        <v>179.9999999988429</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000115829801</v>
+        <v>0.9526279646110868</v>
       </c>
       <c r="O6">
-        <v>0.5500000122512997</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.10000002383428</v>
+        <v>0.9526279649968783</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999965509</v>
+        <v>1.148870050138599E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999965523</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>7.278401917391686E-13</v>
+        <v>179.9999999988429</v>
       </c>
     </row>
   </sheetData>
@@ -1172,13 +1172,13 @@
         <v>1.109634423210917</v>
       </c>
       <c r="O3">
-        <v>0.7617779018710715</v>
+        <v>0.7617779018710716</v>
       </c>
       <c r="P3">
-        <v>0.9348070984869523</v>
+        <v>0.9348070984869525</v>
       </c>
       <c r="Q3">
-        <v>19.43181595267037</v>
+        <v>19.43181595267036</v>
       </c>
       <c r="R3">
         <v>-104.2565908665021</v>
@@ -1216,28 +1216,28 @@
         <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162184</v>
+        <v>0.6277319163162197</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639744</v>
+        <v>0.6277319163639754</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
         <v>1.075852895209832</v>
       </c>
       <c r="O4">
-        <v>0.623345263255181</v>
+        <v>0.6233452632551811</v>
       </c>
       <c r="P4">
         <v>0.9229411060011539</v>
       </c>
       <c r="Q4">
-        <v>16.25665454943075</v>
+        <v>16.25665454943074</v>
       </c>
       <c r="R4">
         <v>-104.9129785376843</v>
@@ -1287,22 +1287,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8641406623245682</v>
+        <v>1.075852895122449</v>
       </c>
       <c r="O5">
-        <v>0.6641535346773524</v>
+        <v>0.6233452631755219</v>
       </c>
       <c r="P5">
-        <v>1.100000023838382</v>
+        <v>0.9229411060761137</v>
       </c>
       <c r="Q5">
-        <v>-142.8672784161505</v>
+        <v>16.25665454976669</v>
       </c>
       <c r="R5">
-        <v>128.2389811397165</v>
+        <v>-104.9129785233392</v>
       </c>
       <c r="S5">
-        <v>-1.252018678445735E-13</v>
+        <v>160.9543898314649</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8641406623245681</v>
+        <v>1.075852895122449</v>
       </c>
       <c r="O6">
-        <v>0.6641535346773524</v>
+        <v>0.6233452631755219</v>
       </c>
       <c r="P6">
-        <v>1.100000023838383</v>
+        <v>0.9229411060761137</v>
       </c>
       <c r="Q6">
-        <v>-142.8672784161505</v>
+        <v>16.25665454976669</v>
       </c>
       <c r="R6">
-        <v>128.2389811397165</v>
+        <v>-104.9129785233392</v>
       </c>
       <c r="S6">
-        <v>-1.318793007962841E-13</v>
+        <v>160.9543898314649</v>
       </c>
     </row>
   </sheetData>
@@ -1533,16 +1533,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.109634423210917</v>
+        <v>1.109634423210918</v>
       </c>
       <c r="O3">
-        <v>0.7617779018710716</v>
+        <v>0.7617779018710719</v>
       </c>
       <c r="P3">
         <v>0.9348070984869523</v>
       </c>
       <c r="Q3">
-        <v>19.43181595267037</v>
+        <v>19.43181595267038</v>
       </c>
       <c r="R3">
         <v>-104.2565908665021</v>
@@ -1559,28 +1559,28 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.763086650675505</v>
+        <v>1.763086650675506</v>
       </c>
       <c r="D4">
-        <v>1.763086650675505</v>
+        <v>1.763086650675506</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20.35837104744277</v>
+        <v>20.35837104744278</v>
       </c>
       <c r="G4">
-        <v>20.35837104744277</v>
+        <v>20.35837104744278</v>
       </c>
       <c r="H4">
         <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162197</v>
+        <v>0.6277319163162202</v>
       </c>
       <c r="K4">
         <v>2.898438697979807</v>
@@ -1595,13 +1595,13 @@
         <v>1.075852895209832</v>
       </c>
       <c r="O4">
-        <v>0.623345263255181</v>
+        <v>0.6233452632551814</v>
       </c>
       <c r="P4">
-        <v>0.922941106001154</v>
+        <v>0.9229411060011539</v>
       </c>
       <c r="Q4">
-        <v>16.25665454943075</v>
+        <v>16.25665454943076</v>
       </c>
       <c r="R4">
         <v>-104.9129785376843</v>
@@ -1651,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8641406623180193</v>
+        <v>1.075852895118288</v>
       </c>
       <c r="O5">
-        <v>0.6641535346805324</v>
+        <v>0.6233452631717288</v>
       </c>
       <c r="P5">
-        <v>1.100000023838382</v>
+        <v>0.9229411060796833</v>
       </c>
       <c r="Q5">
-        <v>-142.867278415948</v>
+        <v>16.25665454978271</v>
       </c>
       <c r="R5">
-        <v>128.2389811402763</v>
+        <v>-104.9129785226561</v>
       </c>
       <c r="S5">
-        <v>-1.268712260825012E-13</v>
+        <v>160.954389831599</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1710,22 +1710,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8641406623180194</v>
+        <v>1.075852895118288</v>
       </c>
       <c r="O6">
-        <v>0.6641535346805324</v>
+        <v>0.6233452631717288</v>
       </c>
       <c r="P6">
-        <v>1.100000023838382</v>
+        <v>0.9229411060796833</v>
       </c>
       <c r="Q6">
-        <v>-142.867278415948</v>
+        <v>16.25665454978271</v>
       </c>
       <c r="R6">
-        <v>128.2389811402763</v>
+        <v>-104.9129785226561</v>
       </c>
       <c r="S6">
-        <v>-1.268712260825012E-13</v>
+        <v>160.954389831599</v>
       </c>
     </row>
   </sheetData>
@@ -1841,7 +1841,7 @@
         <v>0.9821968591989456</v>
       </c>
       <c r="O2">
-        <v>0.8500049525414021</v>
+        <v>0.850004952541402</v>
       </c>
       <c r="P2">
         <v>0.9468598309457217</v>
@@ -1897,16 +1897,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9900703401370795</v>
+        <v>0.990070340137079</v>
       </c>
       <c r="O3">
-        <v>0.3617201835030114</v>
+        <v>0.3617201835030111</v>
       </c>
       <c r="P3">
         <v>0.7649715466411121</v>
       </c>
       <c r="Q3">
-        <v>8.150888684274479</v>
+        <v>8.150888684274465</v>
       </c>
       <c r="R3">
         <v>-129.0915432241893</v>
@@ -1923,49 +1923,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.119085825515527</v>
+        <v>3.119085825515526</v>
       </c>
       <c r="D4">
-        <v>3.119085825515527</v>
+        <v>3.119085825515526</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36.01610081973871</v>
+        <v>36.0161008197387</v>
       </c>
       <c r="G4">
-        <v>36.01610081973871</v>
+        <v>36.0161008197387</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.8660254037880056</v>
+        <v>0.8660254037880054</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037883347</v>
+        <v>0.8660254037883346</v>
       </c>
       <c r="Q4">
-        <v>1.723504241635272E-10</v>
+        <v>1.72333885432898E-10</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999996985028</v>
+        <v>0.8660254036128876</v>
       </c>
       <c r="O5">
-        <v>0.5000000003057973</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634524</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999959872</v>
+        <v>1.336740181848983E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>7.877701695466383E-13</v>
+        <v>179.999999998655</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999996985028</v>
+        <v>0.8660254036128876</v>
       </c>
       <c r="O6">
-        <v>0.5000000003057974</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634523</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999959872</v>
+        <v>1.336736803305169E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>7.877701695466381E-13</v>
+        <v>179.999999998655</v>
       </c>
     </row>
   </sheetData>
@@ -2205,7 +2205,7 @@
         <v>0.9821968591989456</v>
       </c>
       <c r="O2">
-        <v>0.8500049525414021</v>
+        <v>0.850004952541402</v>
       </c>
       <c r="P2">
         <v>0.9468598309457217</v>
@@ -2261,16 +2261,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9900703401370795</v>
+        <v>0.990070340137079</v>
       </c>
       <c r="O3">
-        <v>0.3617201835030114</v>
+        <v>0.3617201835030111</v>
       </c>
       <c r="P3">
         <v>0.7649715466411121</v>
       </c>
       <c r="Q3">
-        <v>8.150888684274479</v>
+        <v>8.150888684274465</v>
       </c>
       <c r="R3">
         <v>-129.0915432241893</v>
@@ -2287,49 +2287,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.119085825515527</v>
+        <v>3.119085825515526</v>
       </c>
       <c r="D4">
-        <v>3.119085825515527</v>
+        <v>3.119085825515526</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36.01610081973871</v>
+        <v>36.0161008197387</v>
       </c>
       <c r="G4">
-        <v>36.01610081973871</v>
+        <v>36.0161008197387</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.8660254037880056</v>
+        <v>0.8660254037880054</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037883347</v>
+        <v>0.8660254037883346</v>
       </c>
       <c r="Q4">
-        <v>1.723504241635272E-10</v>
+        <v>1.72333885432898E-10</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999996985028</v>
+        <v>0.8660254036128876</v>
       </c>
       <c r="O5">
-        <v>0.5000000003057973</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634524</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999959872</v>
+        <v>1.336740181848983E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>7.877701695466383E-13</v>
+        <v>179.999999998655</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999996985028</v>
+        <v>0.8660254036128876</v>
       </c>
       <c r="O6">
-        <v>0.5000000003057974</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.0000000000043</v>
+        <v>0.8660254039634523</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999959872</v>
+        <v>1.336736803305169E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999959888</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>7.877701695466381E-13</v>
+        <v>179.999999998655</v>
       </c>
     </row>
   </sheetData>
@@ -2575,7 +2575,7 @@
         <v>0.9681777323222122</v>
       </c>
       <c r="Q2">
-        <v>27.82469744524451</v>
+        <v>27.8246974452445</v>
       </c>
       <c r="R2">
         <v>-92.15705182751169</v>
@@ -2628,13 +2628,13 @@
         <v>1.018434506766488</v>
       </c>
       <c r="O3">
-        <v>0.7086876959566593</v>
+        <v>0.708687695956659</v>
       </c>
       <c r="P3">
-        <v>0.8449321159941328</v>
+        <v>0.8449321159941326</v>
       </c>
       <c r="Q3">
-        <v>19.61176266474869</v>
+        <v>19.61176266474868</v>
       </c>
       <c r="R3">
         <v>-105.2709110729077</v>
@@ -2666,37 +2666,37 @@
         <v>17.53180025040607</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.9573399675119604</v>
+        <v>0.9573399675119605</v>
       </c>
       <c r="O4">
-        <v>0.5367995610775461</v>
+        <v>0.536799561077546</v>
       </c>
       <c r="P4">
-        <v>0.8529812840863317</v>
+        <v>0.8529812840863316</v>
       </c>
       <c r="Q4">
-        <v>15.93288697155596</v>
+        <v>15.93288697155595</v>
       </c>
       <c r="R4">
-        <v>-101.7238138495563</v>
+        <v>-101.7238138495564</v>
       </c>
       <c r="S4">
         <v>162.0554462537874</v>
@@ -2743,22 +2743,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7487167004860205</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O5">
-        <v>0.6096342801113654</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P5">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q5">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R5">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S5">
-        <v>4.039847023318874E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2802,22 +2802,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7487167004860205</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O6">
-        <v>0.6096342801113654</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P6">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q6">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R6">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S6">
-        <v>4.223476433469732E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
   </sheetData>
@@ -2939,7 +2939,7 @@
         <v>0.9681777323222122</v>
       </c>
       <c r="Q2">
-        <v>27.82469744524451</v>
+        <v>27.8246974452445</v>
       </c>
       <c r="R2">
         <v>-92.15705182751169</v>
@@ -2992,13 +2992,13 @@
         <v>1.018434506766488</v>
       </c>
       <c r="O3">
-        <v>0.7086876959566593</v>
+        <v>0.708687695956659</v>
       </c>
       <c r="P3">
-        <v>0.8449321159941328</v>
+        <v>0.8449321159941326</v>
       </c>
       <c r="Q3">
-        <v>19.61176266474869</v>
+        <v>19.61176266474868</v>
       </c>
       <c r="R3">
         <v>-105.2709110729077</v>
@@ -3030,37 +3030,37 @@
         <v>17.53180025040607</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.9573399675119604</v>
+        <v>0.9573399675119605</v>
       </c>
       <c r="O4">
-        <v>0.5367995610775461</v>
+        <v>0.536799561077546</v>
       </c>
       <c r="P4">
-        <v>0.8529812840863317</v>
+        <v>0.8529812840863316</v>
       </c>
       <c r="Q4">
-        <v>15.93288697155596</v>
+        <v>15.93288697155595</v>
       </c>
       <c r="R4">
-        <v>-101.7238138495563</v>
+        <v>-101.7238138495564</v>
       </c>
       <c r="S4">
         <v>162.0554462537874</v>
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7487167004860205</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O5">
-        <v>0.6096342801113654</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P5">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q5">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R5">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S5">
-        <v>4.039847023318874E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3166,22 +3166,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7487167004860205</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O6">
-        <v>0.6096342801113654</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P6">
-        <v>1.000000000003612</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q6">
-        <v>-142.5584264921974</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R6">
-        <v>131.6989175487492</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S6">
-        <v>4.223476433469732E-14</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
   </sheetData>
@@ -3309,7 +3309,7 @@
         <v>30.27740992635148</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
         <v>145.833649147256</v>
@@ -3359,19 +3359,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6205467346737962</v>
+        <v>0.6205467346737964</v>
       </c>
       <c r="O3">
         <v>1.100000023851052</v>
       </c>
       <c r="P3">
-        <v>0.9549975894344676</v>
+        <v>0.9549975894344678</v>
       </c>
       <c r="Q3">
-        <v>30.02212424388602</v>
+        <v>30.02212424388601</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999649</v>
+        <v>-89.99999999999646</v>
       </c>
       <c r="S3">
         <v>124.2363583956003</v>
@@ -3385,7 +3385,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.149403058432903</v>
+        <v>4.149403058432901</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>47.91317945524987</v>
+        <v>47.91317945524984</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3409,37 +3409,37 @@
         <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162184</v>
+        <v>0.6277319163162197</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639744</v>
+        <v>0.6277319163639754</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.5038029474387162</v>
+        <v>0.5038029474387166</v>
       </c>
       <c r="O4">
         <v>1.100000023851052</v>
       </c>
       <c r="P4">
-        <v>0.8521527588186366</v>
+        <v>0.8521527588186368</v>
       </c>
       <c r="Q4">
-        <v>41.72313523393701</v>
+        <v>41.72313523393696</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999625</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S4">
-        <v>116.1844690692804</v>
+        <v>116.1844690692805</v>
       </c>
       <c r="T4">
-        <v>4.149403058432902</v>
+        <v>4.149403058432901</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8566350060579376</v>
+        <v>0.5038029475324128</v>
       </c>
       <c r="O5">
-        <v>1.098257914917705</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P5">
-        <v>0.4999878050007193</v>
+        <v>0.8521527586165761</v>
       </c>
       <c r="Q5">
-        <v>-104.6805795097902</v>
+        <v>41.72313525482284</v>
       </c>
       <c r="R5">
-        <v>101.400975717282</v>
+        <v>-89.99999999999565</v>
       </c>
       <c r="S5">
-        <v>-29.72566761418703</v>
+        <v>116.1844690720437</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3545,22 +3545,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8566350060579375</v>
+        <v>0.5038029475324127</v>
       </c>
       <c r="O6">
-        <v>1.098257914917705</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P6">
-        <v>0.4999878050007191</v>
+        <v>0.8521527586165762</v>
       </c>
       <c r="Q6">
-        <v>-104.6805795097902</v>
+        <v>41.72313525482284</v>
       </c>
       <c r="R6">
-        <v>101.4009757172819</v>
+        <v>-89.99999999999567</v>
       </c>
       <c r="S6">
-        <v>-29.72566761418705</v>
+        <v>116.1844690720437</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3741,19 +3741,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6205467346737963</v>
+        <v>0.6205467346737967</v>
       </c>
       <c r="O3">
         <v>1.100000023851052</v>
       </c>
       <c r="P3">
-        <v>0.9549975894344674</v>
+        <v>0.9549975894344676</v>
       </c>
       <c r="Q3">
-        <v>30.02212424388602</v>
+        <v>30.02212424388603</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S3">
         <v>124.2363583956003</v>
@@ -3767,7 +3767,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.149403058432901</v>
+        <v>4.149403058432897</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>47.91317945524984</v>
+        <v>47.91317945524979</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3788,10 +3788,10 @@
         <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162197</v>
+        <v>0.6277319163162202</v>
       </c>
       <c r="K4">
         <v>2.898438697979807</v>
@@ -3803,25 +3803,25 @@
         <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.5038029474387163</v>
+        <v>0.5038029474387168</v>
       </c>
       <c r="O4">
         <v>1.100000023851052</v>
       </c>
       <c r="P4">
-        <v>0.8521527588186363</v>
+        <v>0.8521527588186364</v>
       </c>
       <c r="Q4">
         <v>41.72313523393699</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999622</v>
+        <v>-89.99999999999625</v>
       </c>
       <c r="S4">
         <v>116.1844690692805</v>
       </c>
       <c r="T4">
-        <v>4.149403058432901</v>
+        <v>4.149403058432897</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8566350060628775</v>
+        <v>0.5038029475368763</v>
       </c>
       <c r="O5">
-        <v>1.098257914912045</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P5">
-        <v>0.4999878049927855</v>
+        <v>0.8521527586069543</v>
       </c>
       <c r="Q5">
-        <v>-104.6805795096043</v>
+        <v>41.72313525581745</v>
       </c>
       <c r="R5">
-        <v>101.400975717265</v>
+        <v>-89.99999999999568</v>
       </c>
       <c r="S5">
-        <v>-29.7256676132589</v>
+        <v>116.1844690721753</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3927,22 +3927,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8566350060628778</v>
+        <v>0.5038029475368763</v>
       </c>
       <c r="O6">
-        <v>1.098257914912045</v>
+        <v>1.100000023851021</v>
       </c>
       <c r="P6">
-        <v>0.4999878049927856</v>
+        <v>0.8521527586069543</v>
       </c>
       <c r="Q6">
-        <v>-104.6805795096043</v>
+        <v>41.72313525581745</v>
       </c>
       <c r="R6">
-        <v>101.400975717265</v>
+        <v>-89.99999999999569</v>
       </c>
       <c r="S6">
-        <v>-29.72566761325888</v>
+        <v>116.1844690721753</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4132,13 +4132,13 @@
         <v>1.055630524129933</v>
       </c>
       <c r="Q3">
-        <v>28.6953408775323</v>
+        <v>28.69534087753231</v>
       </c>
       <c r="R3">
         <v>-89.99999999999643</v>
       </c>
       <c r="S3">
-        <v>142.6235429121603</v>
+        <v>142.6235429121604</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4173,19 +4173,19 @@
         <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162184</v>
+        <v>0.6277319163162197</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639744</v>
+        <v>0.6277319163639754</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.9132295418291418</v>
+        <v>0.9132295418291422</v>
       </c>
       <c r="O4">
         <v>1.100000023844968</v>
@@ -4247,22 +4247,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.009027019302548</v>
+        <v>0.9132295418366296</v>
       </c>
       <c r="O5">
-        <v>1.103502265351497</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P5">
-        <v>0.9174450355526041</v>
+        <v>1.016646408559263</v>
       </c>
       <c r="Q5">
-        <v>-116.8493087016271</v>
+        <v>30.19334881017324</v>
       </c>
       <c r="R5">
-        <v>114.3920679454525</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S5">
-        <v>-6.556290856891482</v>
+        <v>140.9330581990972</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4309,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.009027019302548</v>
+        <v>0.9132295418366296</v>
       </c>
       <c r="O6">
-        <v>1.103502265351497</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P6">
-        <v>0.9174450355526041</v>
+        <v>1.016646408559263</v>
       </c>
       <c r="Q6">
-        <v>-116.8493087016271</v>
+        <v>30.19334881017324</v>
       </c>
       <c r="R6">
-        <v>114.3920679454526</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S6">
-        <v>-6.556290856891478</v>
+        <v>140.9330581990972</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.938031900955419</v>
+        <v>0.9380319009554192</v>
       </c>
       <c r="G2">
-        <v>-1.13019952195246</v>
+        <v>-1.130199521952444</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.2917056037382958</v>
+        <v>0.291705603738296</v>
       </c>
       <c r="G3">
-        <v>-29.1713773552606</v>
+        <v>-29.17137735526025</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4420,16 +4420,16 @@
         <v>148.3661769587498</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354127</v>
+        <v>0.6277319163354106</v>
       </c>
       <c r="E4">
-        <v>2.89843869796006</v>
+        <v>2.898438697960061</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>77.77984578051343</v>
+        <v>77.77984578051347</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9563222180694877</v>
+        <v>0.9563222180694876</v>
       </c>
       <c r="O3">
-        <v>1.100000023844967</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P3">
-        <v>1.055630524129933</v>
+        <v>1.055630524129932</v>
       </c>
       <c r="Q3">
-        <v>28.69534087753229</v>
+        <v>28.69534087753231</v>
       </c>
       <c r="R3">
         <v>-89.99999999999643</v>
       </c>
       <c r="S3">
-        <v>142.6235429121604</v>
+        <v>142.6235429121603</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.259771140028916</v>
+        <v>1.259771140028915</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4700,10 +4700,10 @@
         <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162197</v>
+        <v>0.6277319163162202</v>
       </c>
       <c r="K4">
         <v>2.898438697979807</v>
@@ -4718,22 +4718,22 @@
         <v>0.9132295418291418</v>
       </c>
       <c r="O4">
-        <v>1.100000023844967</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P4">
         <v>1.016646408614733</v>
       </c>
       <c r="Q4">
-        <v>30.19334880627418</v>
+        <v>30.19334880627419</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999633</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
         <v>140.9330581974619</v>
       </c>
       <c r="T4">
-        <v>1.259771140028916</v>
+        <v>1.259771140028915</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4777,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.00902701930365</v>
+        <v>0.9132295418369862</v>
       </c>
       <c r="O5">
-        <v>1.103502265349777</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P5">
-        <v>0.9174450355508896</v>
+        <v>1.016646408556622</v>
       </c>
       <c r="Q5">
-        <v>-116.8493087015521</v>
+        <v>30.19334881035892</v>
       </c>
       <c r="R5">
-        <v>114.3920679454542</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S5">
-        <v>-6.556290856705079</v>
+        <v>140.9330581991751</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4839,22 +4839,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.00902701930365</v>
+        <v>0.9132295418369862</v>
       </c>
       <c r="O6">
-        <v>1.103502265349776</v>
+        <v>1.100000023844961</v>
       </c>
       <c r="P6">
-        <v>0.9174450355508897</v>
+        <v>1.016646408556622</v>
       </c>
       <c r="Q6">
-        <v>-116.8493087015521</v>
+        <v>30.19334881035892</v>
       </c>
       <c r="R6">
-        <v>114.3920679454542</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S6">
-        <v>-6.556290856705076</v>
+        <v>140.9330581991751</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5035,13 +5035,13 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6800187783876562</v>
+        <v>0.6800187783876563</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994824</v>
       </c>
       <c r="P3">
-        <v>0.9802656726501163</v>
+        <v>0.9802656726501165</v>
       </c>
       <c r="Q3">
         <v>21.6381347987348</v>
@@ -5061,7 +5061,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.826014555890702</v>
+        <v>2.826014555890701</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5070,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>32.63200529154595</v>
+        <v>32.63200529154594</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5079,43 +5079,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.5470567493003651</v>
+        <v>0.5470567493003653</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994824</v>
       </c>
       <c r="P4">
         <v>0.8611554265665963</v>
       </c>
       <c r="Q4">
-        <v>30.64462611762083</v>
+        <v>30.64462611762082</v>
       </c>
       <c r="R4">
         <v>-89.99999999999622</v>
       </c>
       <c r="S4">
-        <v>123.1301085477829</v>
+        <v>123.130108547783</v>
       </c>
       <c r="T4">
-        <v>2.826014555890702</v>
+        <v>2.8260145558907</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202072</v>
       </c>
       <c r="O5">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P5">
-        <v>0.6004774519284555</v>
+        <v>0.8611554264093794</v>
       </c>
       <c r="Q5">
-        <v>-110.2053565287608</v>
+        <v>30.6446261341906</v>
       </c>
       <c r="R5">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999544</v>
       </c>
       <c r="S5">
-        <v>-25.16850627980606</v>
+        <v>123.1301085495603</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5221,22 +5221,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202072</v>
       </c>
       <c r="O6">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P6">
-        <v>0.6004774519284556</v>
+        <v>0.8611554264093793</v>
       </c>
       <c r="Q6">
-        <v>-110.2053565287608</v>
+        <v>30.64462613419058</v>
       </c>
       <c r="R6">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999545</v>
       </c>
       <c r="S6">
-        <v>-25.16850627980606</v>
+        <v>123.1301085495602</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5417,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6800187783876562</v>
+        <v>0.6800187783876563</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994824</v>
       </c>
       <c r="P3">
-        <v>0.9802656726501163</v>
+        <v>0.9802656726501165</v>
       </c>
       <c r="Q3">
         <v>21.6381347987348</v>
@@ -5443,7 +5443,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.826014555890702</v>
+        <v>2.826014555890701</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>32.63200529154595</v>
+        <v>32.63200529154594</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5461,43 +5461,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.5470567493003651</v>
+        <v>0.5470567493003653</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994826</v>
+        <v>0.9999999999994824</v>
       </c>
       <c r="P4">
         <v>0.8611554265665963</v>
       </c>
       <c r="Q4">
-        <v>30.64462611762083</v>
+        <v>30.64462611762082</v>
       </c>
       <c r="R4">
         <v>-89.99999999999622</v>
       </c>
       <c r="S4">
-        <v>123.1301085477829</v>
+        <v>123.130108547783</v>
       </c>
       <c r="T4">
-        <v>2.826014555890702</v>
+        <v>2.8260145558907</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202072</v>
       </c>
       <c r="O5">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P5">
-        <v>0.6004774519284555</v>
+        <v>0.8611554264093794</v>
       </c>
       <c r="Q5">
-        <v>-110.2053565287608</v>
+        <v>30.6446261341906</v>
       </c>
       <c r="R5">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999544</v>
       </c>
       <c r="S5">
-        <v>-25.16850627980606</v>
+        <v>123.1301085495603</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7867556811609819</v>
+        <v>0.5470567493202072</v>
       </c>
       <c r="O6">
-        <v>1.03019516757584</v>
+        <v>0.9999999999994506</v>
       </c>
       <c r="P6">
-        <v>0.6004774519284556</v>
+        <v>0.8611554264093793</v>
       </c>
       <c r="Q6">
-        <v>-110.2053565287608</v>
+        <v>30.64462613419058</v>
       </c>
       <c r="R6">
-        <v>105.2938654446194</v>
+        <v>-89.99999999999545</v>
       </c>
       <c r="S6">
-        <v>-25.16850627980606</v>
+        <v>123.1301085495602</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8789265977783918</v>
+        <v>0.8789265977783917</v>
       </c>
       <c r="O3">
-        <v>0.9999999999998958</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P3">
         <v>0.9728049023577379</v>
       </c>
       <c r="Q3">
-        <v>28.03324723559999</v>
+        <v>28.03324723559998</v>
       </c>
       <c r="R3">
         <v>-89.99999999999643</v>
@@ -5843,34 +5843,34 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
         <v>0.834378493082676</v>
       </c>
       <c r="O4">
-        <v>0.9999999999998958</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P4">
-        <v>0.9184277367072737</v>
+        <v>0.9184277367072738</v>
       </c>
       <c r="Q4">
-        <v>30.72819116678025</v>
+        <v>30.72819116678024</v>
       </c>
       <c r="R4">
         <v>-89.99999999999631</v>
@@ -5923,22 +5923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O5">
-        <v>0.9984707549023011</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P5">
-        <v>0.8325450847440358</v>
+        <v>0.9184277366570416</v>
       </c>
       <c r="Q5">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073054</v>
       </c>
       <c r="R5">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S5">
-        <v>-5.863816409929016</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O6">
-        <v>0.9984707549023011</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P6">
-        <v>0.8325450847440359</v>
+        <v>0.9184277366570414</v>
       </c>
       <c r="Q6">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073053</v>
       </c>
       <c r="R6">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S6">
-        <v>-5.863816409929017</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6181,16 +6181,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8789265977783918</v>
+        <v>0.8789265977783917</v>
       </c>
       <c r="O3">
-        <v>0.9999999999998958</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P3">
         <v>0.9728049023577379</v>
       </c>
       <c r="Q3">
-        <v>28.03324723559999</v>
+        <v>28.03324723559998</v>
       </c>
       <c r="R3">
         <v>-89.99999999999643</v>
@@ -6225,34 +6225,34 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
         <v>0.834378493082676</v>
       </c>
       <c r="O4">
-        <v>0.9999999999998958</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P4">
-        <v>0.9184277367072737</v>
+        <v>0.9184277367072738</v>
       </c>
       <c r="Q4">
-        <v>30.72819116678025</v>
+        <v>30.72819116678024</v>
       </c>
       <c r="R4">
         <v>-89.99999999999631</v>
@@ -6305,22 +6305,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O5">
-        <v>0.9984707549023011</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P5">
-        <v>0.8325450847440358</v>
+        <v>0.9184277366570416</v>
       </c>
       <c r="Q5">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073054</v>
       </c>
       <c r="R5">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S5">
-        <v>-5.863816409929016</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6367,22 +6367,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9217493209491633</v>
+        <v>0.8343784930929388</v>
       </c>
       <c r="O6">
-        <v>0.9984707549023011</v>
+        <v>0.9999999999998829</v>
       </c>
       <c r="P6">
-        <v>0.8325450847440359</v>
+        <v>0.9184277366570414</v>
       </c>
       <c r="Q6">
-        <v>-116.6954725072258</v>
+        <v>30.72819117073053</v>
       </c>
       <c r="R6">
-        <v>114.5022283388587</v>
+        <v>-89.99999999999602</v>
       </c>
       <c r="S6">
-        <v>-5.863816409929017</v>
+        <v>141.3462823818687</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6513,7 +6513,7 @@
         <v>25.29952259328411</v>
       </c>
       <c r="R2">
-        <v>-91.13019952198896</v>
+        <v>-91.13019952198897</v>
       </c>
       <c r="S2">
         <v>151.4964745421679</v>
@@ -6566,13 +6566,13 @@
         <v>0.8815655946738199</v>
       </c>
       <c r="O3">
-        <v>0.2917056037516216</v>
+        <v>0.291705603751622</v>
       </c>
       <c r="P3">
-        <v>0.7906583687018803</v>
+        <v>0.7906583687018802</v>
       </c>
       <c r="Q3">
-        <v>-1.718458463499447</v>
+        <v>-1.71845846349945</v>
       </c>
       <c r="R3">
         <v>-119.1713773545954</v>
@@ -6592,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.02692572606477</v>
+        <v>5.026925726064771</v>
       </c>
       <c r="D4">
         <v>2.971978874802879</v>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>58.04593842279501</v>
+        <v>58.04593842279502</v>
       </c>
       <c r="G4">
         <v>34.31745606786647</v>
@@ -6613,16 +6613,16 @@
         <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162184</v>
+        <v>0.6277319163162197</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639744</v>
+        <v>0.6277319163639754</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
         <v>0.7575177917545732</v>
@@ -6631,10 +6631,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7575177917593718</v>
+        <v>0.7575177917593717</v>
       </c>
       <c r="Q4">
-        <v>-12.52501517673264</v>
+        <v>-12.52501517673265</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4373531006292007</v>
+        <v>0.7575177915084544</v>
       </c>
       <c r="O5">
-        <v>0.4373531012715692</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8747062019007699</v>
+        <v>0.7575177918792887</v>
       </c>
       <c r="Q5">
-        <v>167.4749848231526</v>
+        <v>-12.5250151735059</v>
       </c>
       <c r="R5">
-        <v>167.4749848331493</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-12.52501517184174</v>
+        <v>167.4749848298125</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6749,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4373531006292004</v>
+        <v>0.7575177915084543</v>
       </c>
       <c r="O6">
-        <v>0.4373531012715696</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8747062019007699</v>
+        <v>0.7575177918792887</v>
       </c>
       <c r="Q6">
-        <v>167.4749848231526</v>
+        <v>-12.5250151735059</v>
       </c>
       <c r="R6">
-        <v>167.4749848331493</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-12.52501517184175</v>
+        <v>167.4749848298125</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6948,13 +6948,13 @@
         <v>0.8815655946738202</v>
       </c>
       <c r="O3">
-        <v>0.2917056037516218</v>
+        <v>0.2917056037516221</v>
       </c>
       <c r="P3">
         <v>0.7906583687018804</v>
       </c>
       <c r="Q3">
-        <v>-1.718458463499447</v>
+        <v>-1.718458463499428</v>
       </c>
       <c r="R3">
         <v>-119.1713773545954</v>
@@ -6974,28 +6974,28 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.026925726064772</v>
+        <v>5.026925726064777</v>
       </c>
       <c r="D4">
-        <v>2.97197887480288</v>
+        <v>2.971978874802878</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>58.04593842279503</v>
+        <v>58.04593842279507</v>
       </c>
       <c r="G4">
-        <v>34.31745606786647</v>
+        <v>34.31745606786646</v>
       </c>
       <c r="H4">
         <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162197</v>
+        <v>0.6277319163162202</v>
       </c>
       <c r="K4">
         <v>2.898438697979807</v>
@@ -7016,7 +7016,7 @@
         <v>0.7575177917593722</v>
       </c>
       <c r="Q4">
-        <v>-12.52501517673264</v>
+        <v>-12.52501517673263</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>167.4749848232924</v>
       </c>
       <c r="T4">
-        <v>3.629597114345203</v>
+        <v>3.629597114345206</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4373531006123705</v>
+        <v>0.757517791496734</v>
       </c>
       <c r="O5">
-        <v>0.4373531012849295</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8747062018973001</v>
+        <v>0.7575177918849991</v>
       </c>
       <c r="Q5">
-        <v>167.4749848231493</v>
+        <v>-12.5250151733523</v>
       </c>
       <c r="R5">
-        <v>167.4749848336167</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-12.52501517160972</v>
+        <v>167.474984830123</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7131,22 +7131,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4373531006123705</v>
+        <v>0.7575177914967343</v>
       </c>
       <c r="O6">
-        <v>0.4373531012849298</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8747062018973002</v>
+        <v>0.7575177918849991</v>
       </c>
       <c r="Q6">
-        <v>167.4749848231493</v>
+        <v>-12.52501517335229</v>
       </c>
       <c r="R6">
-        <v>167.4749848336167</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-12.52501517160973</v>
+        <v>167.474984830123</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7330,13 +7330,13 @@
         <v>1.049401079162727</v>
       </c>
       <c r="O3">
-        <v>0.891057042039974</v>
+        <v>0.8910570420399742</v>
       </c>
       <c r="P3">
         <v>0.9642317969850345</v>
       </c>
       <c r="Q3">
-        <v>21.91294083447449</v>
+        <v>21.9129408344745</v>
       </c>
       <c r="R3">
         <v>-99.16867920487518</v>
@@ -7359,7 +7359,7 @@
         <v>1.382520063921417</v>
       </c>
       <c r="D4">
-        <v>1.176705138709485</v>
+        <v>1.176705138709486</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7368,7 +7368,7 @@
         <v>15.96396662130177</v>
       </c>
       <c r="G4">
-        <v>13.58742057181474</v>
+        <v>13.58742057181475</v>
       </c>
       <c r="H4">
         <v>3.698069333823729</v>
@@ -7377,22 +7377,22 @@
         <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162184</v>
+        <v>0.6277319163162197</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639744</v>
+        <v>0.6277319163639754</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
         <v>1.006459707631937</v>
       </c>
       <c r="O4">
-        <v>0.8020156209380068</v>
+        <v>0.802015620938007</v>
       </c>
       <c r="P4">
         <v>0.9269140407833439</v>
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9042880734209771</v>
+        <v>1.006459707571176</v>
       </c>
       <c r="O5">
-        <v>0.8148284578940896</v>
+        <v>0.8020156208867663</v>
       </c>
       <c r="P5">
-        <v>1.01669931770016</v>
+        <v>0.9269140407971426</v>
       </c>
       <c r="Q5">
-        <v>-133.5033356425525</v>
+        <v>20.05417836007251</v>
       </c>
       <c r="R5">
-        <v>118.7983947242826</v>
+        <v>-99.52967389296813</v>
       </c>
       <c r="S5">
-        <v>-3.278220185527791</v>
+        <v>151.2507819007874</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7513,22 +7513,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9042880734209771</v>
+        <v>1.006459707571176</v>
       </c>
       <c r="O6">
-        <v>0.8148284578940899</v>
+        <v>0.8020156208867663</v>
       </c>
       <c r="P6">
-        <v>1.01669931770016</v>
+        <v>0.9269140407971426</v>
       </c>
       <c r="Q6">
-        <v>-133.5033356425525</v>
+        <v>20.05417836007251</v>
       </c>
       <c r="R6">
-        <v>118.7983947242827</v>
+        <v>-99.52967389296813</v>
       </c>
       <c r="S6">
-        <v>-3.278220185527793</v>
+        <v>151.2507819007874</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7712,13 +7712,13 @@
         <v>1.049401079162727</v>
       </c>
       <c r="O3">
-        <v>0.8910570420399738</v>
+        <v>0.8910570420399743</v>
       </c>
       <c r="P3">
-        <v>0.9642317969850346</v>
+        <v>0.9642317969850347</v>
       </c>
       <c r="Q3">
-        <v>21.91294083447449</v>
+        <v>21.9129408344745</v>
       </c>
       <c r="R3">
         <v>-99.16867920487518</v>
@@ -7741,25 +7741,25 @@
         <v>1.382520063921417</v>
       </c>
       <c r="D4">
-        <v>1.176705138709486</v>
+        <v>1.176705138709485</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15.96396662130177</v>
+        <v>15.96396662130178</v>
       </c>
       <c r="G4">
-        <v>13.58742057181475</v>
+        <v>13.58742057181474</v>
       </c>
       <c r="H4">
         <v>3.698069333823729</v>
       </c>
       <c r="I4">
-        <v>1.935851081753642</v>
+        <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162197</v>
+        <v>0.6277319163162202</v>
       </c>
       <c r="K4">
         <v>2.898438697979807</v>
@@ -7771,25 +7771,25 @@
         <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>1.006459707631937</v>
+        <v>1.006459707631938</v>
       </c>
       <c r="O4">
-        <v>0.8020156209380068</v>
+        <v>0.802015620938007</v>
       </c>
       <c r="P4">
         <v>0.9269140407833439</v>
       </c>
       <c r="Q4">
-        <v>20.05417835824807</v>
+        <v>20.05417835824808</v>
       </c>
       <c r="R4">
-        <v>-99.52967390014047</v>
+        <v>-99.52967390014048</v>
       </c>
       <c r="S4">
         <v>151.250781897275</v>
       </c>
       <c r="T4">
-        <v>1.202564331496539</v>
+        <v>1.202564331496538</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7833,22 +7833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9042880734171623</v>
+        <v>1.006459707568283</v>
       </c>
       <c r="O5">
-        <v>0.8148284578941782</v>
+        <v>0.8020156208843262</v>
       </c>
       <c r="P5">
-        <v>1.016699317699292</v>
+        <v>0.9269140407977997</v>
       </c>
       <c r="Q5">
-        <v>-133.5033356423602</v>
+        <v>20.05417836015939</v>
       </c>
       <c r="R5">
-        <v>118.7983947246034</v>
+        <v>-99.52967389262659</v>
       </c>
       <c r="S5">
-        <v>-3.278220185449201</v>
+        <v>151.2507819009546</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7895,22 +7895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9042880734171623</v>
+        <v>1.006459707568283</v>
       </c>
       <c r="O6">
-        <v>0.8148284578941782</v>
+        <v>0.8020156208843262</v>
       </c>
       <c r="P6">
-        <v>1.016699317699292</v>
+        <v>0.9269140407977997</v>
       </c>
       <c r="Q6">
-        <v>-133.5033356423602</v>
+        <v>20.05417836015939</v>
       </c>
       <c r="R6">
-        <v>118.7983947246034</v>
+        <v>-99.52967389262659</v>
       </c>
       <c r="S6">
-        <v>-3.278220185449203</v>
+        <v>151.2507819009546</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8032,10 +8032,10 @@
         <v>0.9610470638492223</v>
       </c>
       <c r="O2">
-        <v>0.8500049525398536</v>
+        <v>0.8500049525398535</v>
       </c>
       <c r="P2">
-        <v>0.9457332649312409</v>
+        <v>0.9457332649312407</v>
       </c>
       <c r="Q2">
         <v>24.73981956262405</v>
@@ -8091,19 +8091,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9239910954518991</v>
+        <v>0.9239910954518989</v>
       </c>
       <c r="O3">
-        <v>0.3617201835032898</v>
+        <v>0.3617201835032897</v>
       </c>
       <c r="P3">
-        <v>0.7395562363454176</v>
+        <v>0.7395562363454172</v>
       </c>
       <c r="Q3">
-        <v>1.807833433806277</v>
+        <v>1.807833433806266</v>
       </c>
       <c r="R3">
-        <v>-129.091543224174</v>
+        <v>-129.0915432241741</v>
       </c>
       <c r="S3">
         <v>160.1110426204011</v>
@@ -8120,58 +8120,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.921619256815303</v>
+        <v>3.921619256815302</v>
       </c>
       <c r="D4">
-        <v>2.491243992016263</v>
+        <v>2.491243992016264</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>45.28295867163072</v>
+        <v>45.28295867163069</v>
       </c>
       <c r="G4">
-        <v>28.76640778815255</v>
+        <v>28.76640778815256</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.7592484163866738</v>
+        <v>0.7592484163866737</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7592484163873853</v>
+        <v>0.7592484163873852</v>
       </c>
       <c r="Q4">
-        <v>-8.930089733930956</v>
+        <v>-8.930089733930961</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>171.0699102656344</v>
+        <v>171.0699102656345</v>
       </c>
       <c r="T4">
-        <v>2.063008215864349</v>
+        <v>2.063008215864345</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4383522772526094</v>
+        <v>0.7592484161672616</v>
       </c>
       <c r="O5">
-        <v>0.438352277862627</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8767045551152365</v>
+        <v>0.7592484165194171</v>
       </c>
       <c r="Q5">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767243</v>
       </c>
       <c r="R5">
-        <v>171.0699102703368</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-8.930089731241036</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8277,22 +8277,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4383522772526096</v>
+        <v>0.7592484161672616</v>
       </c>
       <c r="O6">
-        <v>0.4383522778626273</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8767045551152369</v>
+        <v>0.7592484165194168</v>
       </c>
       <c r="Q6">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767245</v>
       </c>
       <c r="R6">
-        <v>171.0699102703368</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-8.930089731241043</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>1.056966443490338</v>
       </c>
       <c r="G2">
-        <v>-1.342925561278414</v>
+        <v>-1.342925561278412</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8371,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8910570420386135</v>
+        <v>0.8910570420386132</v>
       </c>
       <c r="G3">
-        <v>-9.168679204911147</v>
+        <v>-9.16867920491114</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8382,22 +8382,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.309686024696609</v>
+        <v>1.30968602469661</v>
       </c>
       <c r="C4">
-        <v>45.36885473474868</v>
+        <v>45.36885473474869</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354127</v>
+        <v>0.6277319163354117</v>
       </c>
       <c r="E4">
-        <v>2.898438697960062</v>
+        <v>2.898438697960059</v>
       </c>
       <c r="F4">
-        <v>0.8020156209364414</v>
+        <v>0.802015620936441</v>
       </c>
       <c r="G4">
-        <v>45.00000000014395</v>
+        <v>45.00000000014396</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8020156208852064</v>
+        <v>0.802015620885195</v>
       </c>
       <c r="G5">
-        <v>-159.5296738930014</v>
+        <v>-9.529673893007804</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.8020156208852064</v>
+        <v>0.802015620885195</v>
       </c>
       <c r="G6">
-        <v>-159.5296738930014</v>
+        <v>-9.5296738930078</v>
       </c>
     </row>
   </sheetData>
@@ -8562,10 +8562,10 @@
         <v>0.9610470638492223</v>
       </c>
       <c r="O2">
-        <v>0.8500049525398536</v>
+        <v>0.8500049525398535</v>
       </c>
       <c r="P2">
-        <v>0.9457332649312409</v>
+        <v>0.9457332649312407</v>
       </c>
       <c r="Q2">
         <v>24.73981956262405</v>
@@ -8621,19 +8621,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9239910954518991</v>
+        <v>0.9239910954518989</v>
       </c>
       <c r="O3">
-        <v>0.3617201835032898</v>
+        <v>0.3617201835032897</v>
       </c>
       <c r="P3">
-        <v>0.7395562363454176</v>
+        <v>0.7395562363454172</v>
       </c>
       <c r="Q3">
-        <v>1.807833433806277</v>
+        <v>1.807833433806266</v>
       </c>
       <c r="R3">
-        <v>-129.091543224174</v>
+        <v>-129.0915432241741</v>
       </c>
       <c r="S3">
         <v>160.1110426204011</v>
@@ -8650,58 +8650,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.921619256815303</v>
+        <v>3.921619256815302</v>
       </c>
       <c r="D4">
-        <v>2.491243992016263</v>
+        <v>2.491243992016264</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>45.28295867163072</v>
+        <v>45.28295867163069</v>
       </c>
       <c r="G4">
-        <v>28.76640778815255</v>
+        <v>28.76640778815256</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.7592484163866738</v>
+        <v>0.7592484163866737</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7592484163873853</v>
+        <v>0.7592484163873852</v>
       </c>
       <c r="Q4">
-        <v>-8.930089733930956</v>
+        <v>-8.930089733930961</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>171.0699102656344</v>
+        <v>171.0699102656345</v>
       </c>
       <c r="T4">
-        <v>2.063008215864349</v>
+        <v>2.063008215864345</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4383522772526094</v>
+        <v>0.7592484161672616</v>
       </c>
       <c r="O5">
-        <v>0.438352277862627</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8767045551152365</v>
+        <v>0.7592484165194171</v>
       </c>
       <c r="Q5">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767243</v>
       </c>
       <c r="R5">
-        <v>171.0699102703368</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>-8.930089731241036</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4383522772526096</v>
+        <v>0.7592484161672616</v>
       </c>
       <c r="O6">
-        <v>0.4383522778626273</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8767045551152369</v>
+        <v>0.7592484165194168</v>
       </c>
       <c r="Q6">
-        <v>171.0699102671665</v>
+        <v>-8.930089731767245</v>
       </c>
       <c r="R6">
-        <v>171.0699102703368</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>-8.930089731241043</v>
+        <v>171.069910269276</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8947,7 +8947,7 @@
         <v>0.958104579130449</v>
       </c>
       <c r="P2">
-        <v>0.9758418560497758</v>
+        <v>0.9758418560497757</v>
       </c>
       <c r="Q2">
         <v>28.35209815663974</v>
@@ -9003,19 +9003,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9677452209809372</v>
+        <v>0.9677452209809371</v>
       </c>
       <c r="O3">
-        <v>0.81392990312027</v>
+        <v>0.8139299031202697</v>
       </c>
       <c r="P3">
-        <v>0.8831724555034683</v>
+        <v>0.883172455503468</v>
       </c>
       <c r="Q3">
         <v>21.67250194521048</v>
       </c>
       <c r="R3">
-        <v>-99.65273561736713</v>
+        <v>-99.65273561736714</v>
       </c>
       <c r="S3">
         <v>149.7426394539454</v>
@@ -9035,7 +9035,7 @@
         <v>1.210751047633806</v>
       </c>
       <c r="D4">
-        <v>0.9664867210300012</v>
+        <v>0.9664867210300015</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -9047,43 +9047,43 @@
         <v>11.1600273710974</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.9044874322036917</v>
+        <v>0.9044874322036915</v>
       </c>
       <c r="O4">
         <v>0.7019303077933687</v>
       </c>
       <c r="P4">
-        <v>0.8518384756869167</v>
+        <v>0.8518384756869165</v>
       </c>
       <c r="Q4">
-        <v>19.80759473074442</v>
+        <v>19.80759473074443</v>
       </c>
       <c r="R4">
-        <v>-97.63434507042334</v>
+        <v>-97.63434507042335</v>
       </c>
       <c r="S4">
         <v>152.8122609529874</v>
       </c>
       <c r="T4">
-        <v>0.9264880498917319</v>
+        <v>0.9264880498917314</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445332</v>
       </c>
       <c r="O5">
-        <v>0.7345230598571356</v>
+        <v>0.7019303077570289</v>
       </c>
       <c r="P5">
-        <v>0.9300083243828787</v>
+        <v>0.8518384757092761</v>
       </c>
       <c r="Q5">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290829</v>
       </c>
       <c r="R5">
-        <v>121.4858228578011</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S5">
-        <v>-2.94338920055252</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9189,22 +9189,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445331</v>
       </c>
       <c r="O6">
-        <v>0.7345230598571356</v>
+        <v>0.7019303077570289</v>
       </c>
       <c r="P6">
-        <v>0.9300083243828787</v>
+        <v>0.8518384757092761</v>
       </c>
       <c r="Q6">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290829</v>
       </c>
       <c r="R6">
-        <v>121.485822857801</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S6">
-        <v>-2.943389200552522</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9329,7 +9329,7 @@
         <v>0.958104579130449</v>
       </c>
       <c r="P2">
-        <v>0.9758418560497758</v>
+        <v>0.9758418560497757</v>
       </c>
       <c r="Q2">
         <v>28.35209815663974</v>
@@ -9385,19 +9385,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9677452209809372</v>
+        <v>0.9677452209809371</v>
       </c>
       <c r="O3">
-        <v>0.81392990312027</v>
+        <v>0.8139299031202697</v>
       </c>
       <c r="P3">
-        <v>0.8831724555034683</v>
+        <v>0.883172455503468</v>
       </c>
       <c r="Q3">
         <v>21.67250194521048</v>
       </c>
       <c r="R3">
-        <v>-99.65273561736713</v>
+        <v>-99.65273561736714</v>
       </c>
       <c r="S3">
         <v>149.7426394539454</v>
@@ -9417,7 +9417,7 @@
         <v>1.210751047633806</v>
       </c>
       <c r="D4">
-        <v>0.9664867210300012</v>
+        <v>0.9664867210300015</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -9429,43 +9429,43 @@
         <v>11.1600273710974</v>
       </c>
       <c r="H4">
-        <v>7.100317906512648</v>
+        <v>7.100317906512646</v>
       </c>
       <c r="I4">
-        <v>1.94006366223862</v>
+        <v>1.940063662238627</v>
       </c>
       <c r="J4">
-        <v>1.113751880253971</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
         <v>3.006397543748692</v>
       </c>
       <c r="L4">
-        <v>1.113751880233242</v>
+        <v>1.113751880233241</v>
       </c>
       <c r="M4">
-        <v>3.006397543745534</v>
+        <v>3.006397543745535</v>
       </c>
       <c r="N4">
-        <v>0.9044874322036917</v>
+        <v>0.9044874322036915</v>
       </c>
       <c r="O4">
         <v>0.7019303077933687</v>
       </c>
       <c r="P4">
-        <v>0.8518384756869167</v>
+        <v>0.8518384756869165</v>
       </c>
       <c r="Q4">
-        <v>19.80759473074442</v>
+        <v>19.80759473074443</v>
       </c>
       <c r="R4">
-        <v>-97.63434507042334</v>
+        <v>-97.63434507042335</v>
       </c>
       <c r="S4">
         <v>152.8122609529874</v>
       </c>
       <c r="T4">
-        <v>0.9264880498917319</v>
+        <v>0.9264880498917314</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -9509,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445332</v>
       </c>
       <c r="O5">
-        <v>0.7345230598571356</v>
+        <v>0.7019303077570289</v>
       </c>
       <c r="P5">
-        <v>0.9300083243828787</v>
+        <v>0.8518384757092761</v>
       </c>
       <c r="Q5">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290829</v>
       </c>
       <c r="R5">
-        <v>121.4858228578011</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S5">
-        <v>-2.94338920055252</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9571,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.794979780667777</v>
+        <v>0.9044874321445331</v>
       </c>
       <c r="O6">
-        <v>0.7345230598571356</v>
+        <v>0.7019303077570289</v>
       </c>
       <c r="P6">
-        <v>0.9300083243828787</v>
+        <v>0.8518384757092761</v>
       </c>
       <c r="Q6">
-        <v>-133.2938037223171</v>
+        <v>19.80759473290829</v>
       </c>
       <c r="R6">
-        <v>121.485822857801</v>
+        <v>-97.63434506177401</v>
       </c>
       <c r="S6">
-        <v>-2.943389200552522</v>
+        <v>152.8122609563333</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9645,7 +9645,7 @@
         <v>1.056966443490338</v>
       </c>
       <c r="G2">
-        <v>-1.342925561278415</v>
+        <v>-1.342925561278413</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8910570420386132</v>
+        <v>0.8910570420386135</v>
       </c>
       <c r="G3">
-        <v>-9.168679204911154</v>
+        <v>-9.168679204911136</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9676,22 +9676,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.309686024696609</v>
+        <v>1.30968602469661</v>
       </c>
       <c r="C4">
         <v>45.36885473474869</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354127</v>
+        <v>0.6277319163354106</v>
       </c>
       <c r="E4">
-        <v>2.89843869796006</v>
+        <v>2.898438697960061</v>
       </c>
       <c r="F4">
-        <v>0.8020156209364411</v>
+        <v>0.8020156209364414</v>
       </c>
       <c r="G4">
-        <v>45.00000000014394</v>
+        <v>45.00000000014396</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8020156208827658</v>
+        <v>0.8020156208827551</v>
       </c>
       <c r="G5">
-        <v>-159.5296738926599</v>
+        <v>-9.529673892666251</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.8020156208827658</v>
+        <v>0.802015620882755</v>
       </c>
       <c r="G6">
-        <v>-159.5296738926599</v>
+        <v>-9.529673892666253</v>
       </c>
     </row>
   </sheetData>
@@ -9793,7 +9793,7 @@
         <v>0.8500049525313291</v>
       </c>
       <c r="G2">
-        <v>-2.653816313408799</v>
+        <v>-2.653816313408785</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9813,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3617201835011328</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="G3">
-        <v>-39.09154322526825</v>
+        <v>-39.09154322526815</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9824,22 +9824,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3.60161008196943</v>
+        <v>3.601610081969431</v>
       </c>
       <c r="C4">
         <v>124.7634330204672</v>
       </c>
       <c r="D4">
-        <v>1.113751880252861</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>69.67231643316977</v>
+        <v>69.67231643316981</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9941,7 +9941,7 @@
         <v>0.8500049525313291</v>
       </c>
       <c r="G2">
-        <v>-2.653816313408799</v>
+        <v>-2.653816313408785</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9961,10 +9961,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3617201835011328</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="G3">
-        <v>-39.09154322526825</v>
+        <v>-39.09154322526815</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9972,22 +9972,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3.60161008196943</v>
+        <v>3.601610081969431</v>
       </c>
       <c r="C4">
         <v>124.7634330204672</v>
       </c>
       <c r="D4">
-        <v>1.113751880252861</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>69.67231643316977</v>
+        <v>69.67231643316981</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10089,7 +10089,7 @@
         <v>0.9581045791269168</v>
       </c>
       <c r="G2">
-        <v>-1.557899718992046</v>
+        <v>-1.557899718992045</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10112,7 +10112,7 @@
         <v>0.8139299031165274</v>
       </c>
       <c r="G3">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430428</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10126,16 +10126,16 @@
         <v>39.70717444468345</v>
       </c>
       <c r="D4">
-        <v>1.113751880252861</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="G4">
-        <v>44.99999999986811</v>
+        <v>44.99999999986814</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10155,10 +10155,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7019303077532709</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G5">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.7019303077532709</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G6">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
   </sheetData>
@@ -10237,7 +10237,7 @@
         <v>0.9581045791269168</v>
       </c>
       <c r="G2">
-        <v>-1.557899718992046</v>
+        <v>-1.557899718992045</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10260,7 +10260,7 @@
         <v>0.8139299031165274</v>
       </c>
       <c r="G3">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430428</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10274,16 +10274,16 @@
         <v>39.70717444468345</v>
       </c>
       <c r="D4">
-        <v>1.113751880252861</v>
+        <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="G4">
-        <v>44.99999999986811</v>
+        <v>44.99999999986814</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7019303077532709</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G5">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10326,10 +10326,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.7019303077532709</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G6">
-        <v>-157.6343450618433</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
   </sheetData>
@@ -10451,7 +10451,7 @@
         <v>1.053494350468705</v>
       </c>
       <c r="Q2">
-        <v>25.98965116739708</v>
+        <v>25.98965116739707</v>
       </c>
       <c r="R2">
         <v>-91.130199522016</v>
@@ -10507,13 +10507,13 @@
         <v>0.2917056037512938</v>
       </c>
       <c r="P3">
-        <v>0.8906876332644388</v>
+        <v>0.8906876332644384</v>
       </c>
       <c r="Q3">
-        <v>7.091324389062537</v>
+        <v>7.091324389062526</v>
       </c>
       <c r="R3">
-        <v>-119.1713773550798</v>
+        <v>-119.1713773550799</v>
       </c>
       <c r="S3">
         <v>171.7794727726615</v>
@@ -10527,19 +10527,19 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.709154423937068</v>
+        <v>3.70915442393707</v>
       </c>
       <c r="D4">
-        <v>3.709154423937068</v>
+        <v>3.70915442393707</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>42.82962610251915</v>
+        <v>42.82962610251918</v>
       </c>
       <c r="G4">
-        <v>42.82962610251915</v>
+        <v>42.82962610251918</v>
       </c>
       <c r="H4">
         <v>3.698069333823729</v>
@@ -10548,28 +10548,28 @@
         <v>1.935851081753643</v>
       </c>
       <c r="J4">
-        <v>0.6277319163162184</v>
+        <v>0.6277319163162197</v>
       </c>
       <c r="K4">
-        <v>2.898438697979808</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163639744</v>
+        <v>0.6277319163639754</v>
       </c>
       <c r="M4">
-        <v>2.89843869795999</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.9526279648032089</v>
+        <v>0.9526279648032087</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.952627964804756</v>
+        <v>0.9526279648047558</v>
       </c>
       <c r="Q4">
-        <v>-1.251667487785137E-11</v>
+        <v>-1.253685726057565E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000115981057</v>
+        <v>0.9526279646198192</v>
       </c>
       <c r="O5">
-        <v>0.5500000122361739</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.10000002383428</v>
+        <v>0.9526279649881451</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999967092</v>
+        <v>1.096015565453787E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999967106</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>7.311789082150363E-13</v>
+        <v>179.9999999988956</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10678,22 +10678,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000115981056</v>
+        <v>0.9526279646198192</v>
       </c>
       <c r="O6">
-        <v>0.5500000122361741</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.10000002383428</v>
+        <v>0.9526279649881451</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999967092</v>
+        <v>1.096014203775813E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999967107</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>7.211627587874331E-13</v>
+        <v>179.9999999988956</v>
       </c>
     </row>
   </sheetData>
